--- a/rules/CORE-000741/negative/02/data/unit-test-coreid-FB1111-negative-2.xlsx
+++ b/rules/CORE-000741/negative/02/data/unit-test-coreid-FB1111-negative-2.xlsx
@@ -19,9 +19,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -43,7 +41,7 @@
       <i val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +64,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -96,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +126,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -569,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -602,6 +611,230 @@
         <is>
           <t>Error value</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>INTMODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TSVAL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>nonempty</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>INTTYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>TSVAL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>PCLASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>TSPARMCD</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>STYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>TSVAL</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>INTERVENTIONAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ts.xpt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Dataset</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>$STYPE_INTERVENTIONAL</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -859,7 +1092,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="7" t="n"/>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>INTMODEL</t>
         </is>
@@ -869,7 +1102,7 @@
           <t>Actual Number of Subjects</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="13" t="inlineStr">
         <is>
           <t>nonempty</t>
         </is>
@@ -900,7 +1133,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>INTTYPE</t>
         </is>
@@ -910,7 +1143,7 @@
           <t>Adaptive Design</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="12" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
@@ -945,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>PCLASS</t>
         </is>
@@ -986,7 +1219,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>STYPE</t>
         </is>
@@ -996,7 +1229,7 @@
           <t>Planned Maximum Age of Subjects</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>INTERVENTIONAL</t>
         </is>
